--- a/public/cennik/Ziomek_Fish_Cennik_B2B_2026.xlsx
+++ b/public/cennik/Ziomek_Fish_Cennik_B2B_2026.xlsx
@@ -5,24 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Ziomek Fish\CHUDOWA\STRATEGJA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vadym\Projects\sztab\public\cennik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC7A98E7-4B77-4F3C-848B-CB3D3625635B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EF42A9D-1DE9-40BB-9DBE-E360AE5C1D61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cennik" sheetId="1" r:id="rId1"/>
-    <sheet name="Warunki współpracy" sheetId="2" r:id="rId2"/>
-    <sheet name="Kontakt" sheetId="3" r:id="rId3"/>
+    <sheet name="Czudowa Marka" sheetId="1" r:id="rId1"/>
+    <sheet name="Owoce morza" sheetId="2" r:id="rId2"/>
+    <sheet name="Warunki współpracy" sheetId="3" r:id="rId3"/>
+    <sheet name="Kontakt" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="161">
   <si>
     <t>ZIOMEK·FISH  —  CENNIK HURTOWY B2B  ·  Czudowa Marka</t>
   </si>
@@ -124,9 +130,15 @@
     <t>5000g / 3000g</t>
   </si>
   <si>
+    <t>Wiadro 5 L  ·  3 kg netto bez zalewy</t>
+  </si>
+  <si>
     <t>1000g / 600g</t>
   </si>
   <si>
+    <t>Wiaderko 1 L  ·  600 g netto bez zalewy</t>
+  </si>
+  <si>
     <t>POMIDORY  ·  ⚠ ostatnie sztuki — brak dostaw do września 2026</t>
   </si>
   <si>
@@ -136,9 +148,76 @@
     <t>Wiadro 5 L  ·  3 kg netto  ·  ostatnie sztuki</t>
   </si>
   <si>
+    <t>Wiaderko 1 L  ·  600 g netto bez zalewy  ·  ostatnie sztuki</t>
+  </si>
+  <si>
     <t>★  Średni opt — najpopularniejszy tier dla regularnych klientów hurtowych</t>
   </si>
   <si>
+    <t>ZIOMEK·FISH  —  CENNIK HURTOWY B2B  ·  Owoce morza</t>
+  </si>
+  <si>
+    <t>Ceny netto PLN  ·  cena zależy od łącznej ilości owoców morza w zamówieniu (1 szt = 1 kg)  ·  Aktualizacja: 01.06.2026</t>
+  </si>
+  <si>
+    <t>Mały hurt
+&lt; 100 szt</t>
+  </si>
+  <si>
+    <t>Średni hurt  ★
+100 — 300 szt</t>
+  </si>
+  <si>
+    <t>Duży hurt
+≥ 300 szt</t>
+  </si>
+  <si>
+    <t>Szt /
+karton</t>
+  </si>
+  <si>
+    <t>KALMARY  (VAT 23%)</t>
+  </si>
+  <si>
+    <t>Kalmar — stróżka solono-suszona</t>
+  </si>
+  <si>
+    <t>1 kg</t>
+  </si>
+  <si>
+    <t>Karton 10 × 1 kg</t>
+  </si>
+  <si>
+    <t>Kalmar — filet o smaku kraba</t>
+  </si>
+  <si>
+    <t>Kalmar — stróżka z chili i sezamem</t>
+  </si>
+  <si>
+    <t>Kalmar — filet skrzydełka</t>
+  </si>
+  <si>
+    <t>Kalmar — skrzydełka z chili (kawałki)</t>
+  </si>
+  <si>
+    <t>PUTASU  (VAT 5%)</t>
+  </si>
+  <si>
+    <t>Putasu — plasterki solone</t>
+  </si>
+  <si>
+    <t>Putasu — plasterki z chili</t>
+  </si>
+  <si>
+    <t>Putasu — kawałki z chili</t>
+  </si>
+  <si>
+    <t>Filet putasu z chili — Chworościec</t>
+  </si>
+  <si>
+    <t>★  Średni hurt — najczęstszy poziom dla regularnych zamówień  ·  poziom ceny zależy od łącznej ilości owoców morza w całym zamówieniu, nie od pojedynczej pozycji</t>
+  </si>
+  <si>
     <t>WARUNKI WSPÓŁPRACY HURTOWEJ</t>
   </si>
   <si>
@@ -199,6 +278,33 @@
     <t>Tylko paletowo  ·  mix SKU na palecie OK  ·  bez minimum sztuk na palecie</t>
   </si>
   <si>
+    <t>PROGI OWOCE MORZA  ·  wg ilości</t>
+  </si>
+  <si>
+    <t>Mały hurt</t>
+  </si>
+  <si>
+    <t>Łączna ilość owoców morza &lt; 100 szt (1 szt = 1 kg)  ·  najwyższa cena</t>
+  </si>
+  <si>
+    <t>Średni hurt  ★</t>
+  </si>
+  <si>
+    <t>Łączna ilość 100 — 300 szt  ·  cena pośrednia</t>
+  </si>
+  <si>
+    <t>Duży hurt</t>
+  </si>
+  <si>
+    <t>Łączna ilość ≥ 300 szt  ·  najniższa cena — najlepsze warunki</t>
+  </si>
+  <si>
+    <t>Poziom liczony</t>
+  </si>
+  <si>
+    <t>Wg sumy wszystkich owoców morza w zamówieniu, nie pojedynczej pozycji</t>
+  </si>
+  <si>
     <t>DOSTAWA  ·  ODBIÓR</t>
   </si>
   <si>
@@ -241,9 +347,6 @@
     <t>60 dni od daty produkcji</t>
   </si>
   <si>
-    <t>60 dni  ·  ostatnie sztuki, brak dostaw do września 2026</t>
-  </si>
-  <si>
     <t>Paleta 3000g</t>
   </si>
   <si>
@@ -301,7 +404,19 @@
     <t>Stawka VAT</t>
   </si>
   <si>
-    <t>5%  ·  ustawa o VAT, załącznik nr 10</t>
+    <t>Zależnie od grupy produktów (poniżej)</t>
+  </si>
+  <si>
+    <t>Stawka VAT — kalmary</t>
+  </si>
+  <si>
+    <t>23%  ·  produkty z kalmara</t>
+  </si>
+  <si>
+    <t>Stawka VAT — putasu / kiszonki</t>
+  </si>
+  <si>
+    <t>5%  ·  ryby przetworzone i warzywa</t>
   </si>
   <si>
     <t>PKWiU</t>
@@ -404,15 +519,6 @@
   </si>
   <si>
     <t>Dziękujemy za zainteresowanie współpracą z Czudowa Marka  ·  Ziomek Fish Sp. z o.o.</t>
-  </si>
-  <si>
-    <t>Wiadro 5 L  ·  3 kg netto bez zalewy</t>
-  </si>
-  <si>
-    <t>Wiaderko 1 L  ·  600 g netto bez zalewy</t>
-  </si>
-  <si>
-    <t>Wiaderko 1 L  ·  600 g netto bez zalewy  ·  ostatnie sztuki</t>
   </si>
 </sst>
 </file>
@@ -425,65 +531,75 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1F2B4A"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2B4A"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF92400E"/>
       <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF92400E"/>
-      <name val="Arial"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="7">
@@ -496,30 +612,35 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2B4A"/>
+        <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8ECF4"/>
+        <bgColor rgb="FFF9FAFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF9FAFB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF9FAFB"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFEF3C7"/>
+        <bgColor rgb="FFFFFF99"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -557,12 +678,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD1D5DB"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD1D5DB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD1D5DB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD1D5DB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -596,41 +758,136 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFEF3C7"/>
+      <rgbColor rgb="FFE8ECF4"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFD1D5DB"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFF9FAFB"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF6B7280"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF1F2B4A"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF92400E"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF1F2937"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -647,10 +904,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -688,234 +945,128 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -931,7 +1082,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -943,846 +1094,912 @@
     <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
     </row>
     <row r="3" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:8" ht="46.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+    </row>
+    <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>1</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="6">
         <v>15.66</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="7">
         <v>14.79</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="6">
         <v>13.92</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="4">
         <v>125</v>
       </c>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <v>20.13</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>19.010000000000002</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="11">
         <v>17.899999999999999</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="9">
         <v>125</v>
       </c>
-      <c r="H7" s="11"/>
-    </row>
-    <row r="8" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>3</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="6">
         <v>20.13</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="7">
         <v>19.010000000000002</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="6">
         <v>17.899999999999999</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="4">
         <v>125</v>
       </c>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="11">
         <v>20.13</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="12">
         <v>19.010000000000002</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="11">
         <v>17.899999999999999</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="9">
         <v>125</v>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+    </row>
+    <row r="11" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>5</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="6">
         <v>29.12</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="7">
         <v>27.5</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="6">
         <v>25.88</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="4">
         <v>125</v>
       </c>
-      <c r="H11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9">
         <v>6</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="11">
         <v>22.5</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="12">
         <v>21.25</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="11">
         <v>20</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="9">
         <v>125</v>
       </c>
-      <c r="H12" s="11"/>
-    </row>
-    <row r="13" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2">
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="6">
         <v>18.45</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="7">
         <v>17.43</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="6">
         <v>16.399999999999999</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="4">
         <v>125</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+    </row>
+    <row r="15" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>8</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="6">
         <v>27.67</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="7">
         <v>26.13</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="6">
         <v>24.59</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="4">
         <v>125</v>
       </c>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="7">
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="9">
         <v>9</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="11">
         <v>10.35</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E16" s="12">
         <v>9.7799999999999994</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="11">
         <v>9.1999999999999993</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="9">
         <v>432</v>
       </c>
-      <c r="H16" s="11"/>
-    </row>
-    <row r="17" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="H16" s="13"/>
+    </row>
+    <row r="17" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>10</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="6">
         <v>27.67</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="7">
         <v>26.13</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="6">
         <v>24.59</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="4">
         <v>125</v>
       </c>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="7">
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="9">
         <v>11</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="11">
         <v>8.31</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E18" s="12">
         <v>7.85</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="11">
         <v>7.38</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="9">
         <v>432</v>
       </c>
-      <c r="H18" s="11"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-    </row>
-    <row r="20" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="2">
+      <c r="B19" s="22"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+    </row>
+    <row r="20" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>12</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="6">
         <v>29.07</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="7">
         <v>27.45</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="6">
         <v>25.84</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="4">
         <v>125</v>
       </c>
-      <c r="H20" s="6"/>
-    </row>
-    <row r="21" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="9">
         <v>13</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="11">
         <v>14.4</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E21" s="12">
         <v>13.6</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="11">
         <v>12.8</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="9">
         <v>288</v>
       </c>
-      <c r="H21" s="11"/>
-    </row>
-    <row r="22" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2">
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
         <v>14</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="6">
         <v>27.67</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="7">
         <v>26.13</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="6">
         <v>24.59</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="4">
         <v>80</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="7">
+      <c r="H22" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="9">
         <v>15</v>
       </c>
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" s="9">
+      <c r="C23" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="11">
         <v>5.85</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="12">
         <v>5.52</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="11">
         <v>5.2</v>
       </c>
-      <c r="G23" s="7">
+      <c r="G23" s="9">
         <v>432</v>
       </c>
-      <c r="H23" s="11" t="s">
-        <v>127</v>
+      <c r="H23" s="13" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+    </row>
+    <row r="25" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>16</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="6">
+        <v>27.67</v>
+      </c>
+      <c r="E25" s="7">
+        <v>26.13</v>
+      </c>
+      <c r="F25" s="6">
+        <v>24.59</v>
+      </c>
+      <c r="G25" s="4">
+        <v>80</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="9">
+        <v>17</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-    </row>
-    <row r="25" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="2">
-        <v>16</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="4">
-        <v>27.67</v>
-      </c>
-      <c r="E25" s="5">
-        <v>26.13</v>
-      </c>
-      <c r="F25" s="4">
-        <v>24.59</v>
-      </c>
-      <c r="G25" s="2">
-        <v>80</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="7">
-        <v>17</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="9">
+      <c r="D26" s="11">
         <v>5.85</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E26" s="12">
         <v>5.52</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="11">
         <v>5.2</v>
       </c>
-      <c r="G26" s="7">
+      <c r="G26" s="9">
         <v>432</v>
       </c>
-      <c r="H26" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
+      <c r="H26" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28" s="24"/>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D39"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="4" customWidth="1"/>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-    </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>38</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-    </row>
-    <row r="3" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="22"/>
-    </row>
-    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
+    <row r="1" spans="1:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+    </row>
+    <row r="2" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="28" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+    </row>
+    <row r="3" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:8" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="G4" s="14" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
+      <c r="H4" s="14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+    </row>
+    <row r="6" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15">
+        <v>1</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="C6" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="22"/>
-    </row>
-    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="12" t="s">
+      <c r="D6" s="17">
+        <v>89.8</v>
+      </c>
+      <c r="E6" s="18">
+        <v>84.35</v>
+      </c>
+      <c r="F6" s="17">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G6" s="15">
+        <v>10</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="13" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15">
+        <v>2</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
+      <c r="C7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="17">
+        <v>89.8</v>
+      </c>
+      <c r="E7" s="18">
+        <v>84.35</v>
+      </c>
+      <c r="F7" s="17">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G7" s="15">
+        <v>10</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15">
+        <v>3</v>
+      </c>
+      <c r="B8" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C8" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="17">
+        <v>89.8</v>
+      </c>
+      <c r="E8" s="18">
+        <v>84.35</v>
+      </c>
+      <c r="F8" s="17">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="G8" s="15">
+        <v>10</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15">
+        <v>4</v>
+      </c>
+      <c r="B9" s="16" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
+      <c r="C9" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="17">
+        <v>83.15</v>
+      </c>
+      <c r="E9" s="18">
+        <v>78.11</v>
+      </c>
+      <c r="F9" s="17">
+        <v>72.59</v>
+      </c>
+      <c r="G9" s="15">
+        <v>10</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15">
+        <v>5</v>
+      </c>
+      <c r="B10" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C10" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="17">
+        <v>112.58</v>
+      </c>
+      <c r="E10" s="18">
+        <v>105.74</v>
+      </c>
+      <c r="F10" s="17">
+        <v>98.28</v>
+      </c>
+      <c r="G10" s="15">
+        <v>10</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
+      <c r="B11" s="29"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+    </row>
+    <row r="12" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15">
+        <v>6</v>
+      </c>
+      <c r="B12" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C12" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="17">
+        <v>66.52</v>
+      </c>
+      <c r="E12" s="18">
+        <v>62.48</v>
+      </c>
+      <c r="F12" s="17">
+        <v>58.07</v>
+      </c>
+      <c r="G12" s="15">
+        <v>10</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="15">
+        <v>7</v>
+      </c>
+      <c r="B13" s="16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="20" t="s">
+      <c r="C13" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="17">
+        <v>66.52</v>
+      </c>
+      <c r="E13" s="18">
+        <v>62.48</v>
+      </c>
+      <c r="F13" s="17">
+        <v>58.07</v>
+      </c>
+      <c r="G13" s="15">
+        <v>10</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="15">
+        <v>8</v>
+      </c>
+      <c r="B14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="C16" s="22"/>
-    </row>
-    <row r="17" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="12" t="s">
+      <c r="C14" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="17">
+        <v>66.52</v>
+      </c>
+      <c r="E14" s="18">
+        <v>62.48</v>
+      </c>
+      <c r="F14" s="17">
+        <v>58.07</v>
+      </c>
+      <c r="G14" s="15">
+        <v>10</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="15">
+        <v>9</v>
+      </c>
+      <c r="B15" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C15" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="17">
+        <v>70.36</v>
+      </c>
+      <c r="E15" s="18">
+        <v>66.09</v>
+      </c>
+      <c r="F15" s="17">
+        <v>61.43</v>
+      </c>
+      <c r="G15" s="15">
+        <v>10</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="30" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="18" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="22"/>
-    </row>
-    <row r="22" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B27" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="29" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B31" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="22"/>
-    </row>
-    <row r="32" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B33" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="22"/>
-    </row>
-    <row r="38" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>93</v>
-      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B4:C4"/>
+  <mergeCells count="5">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
@@ -1791,8 +2008,349 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+    </row>
+    <row r="3" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C4" s="22"/>
+    </row>
+    <row r="5" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="22"/>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="33"/>
+    </row>
+    <row r="17" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="31"/>
+      <c r="C21" s="31"/>
+    </row>
+    <row r="22" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="20"/>
+    </row>
+    <row r="23" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B27" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" s="20"/>
+    </row>
+    <row r="28" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="32"/>
+    </row>
+    <row r="32" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B32" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33" s="19" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B37" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="C37" s="22"/>
+    </row>
+    <row r="38" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B38" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43" s="20"/>
+    </row>
+    <row r="44" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B44" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B45" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B46" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B47" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B16:C16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -1800,162 +2358,162 @@
     <col min="4" max="4" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-    </row>
-    <row r="2" spans="1:4" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
+    <row r="1" spans="1:4" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+    </row>
+    <row r="2" spans="1:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="4" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="20" t="s">
-        <v>96</v>
+    <row r="4" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="22" t="s">
+        <v>131</v>
       </c>
       <c r="C4" s="22"/>
     </row>
-    <row r="5" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="20" t="s">
-        <v>107</v>
+    <row r="5" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="22" t="s">
+        <v>142</v>
       </c>
       <c r="C11" s="22"/>
     </row>
-    <row r="12" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="20" t="s">
-        <v>118</v>
+    <row r="12" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="22" t="s">
+        <v>153</v>
       </c>
       <c r="C18" s="22"/>
     </row>
-    <row r="19" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B24" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="17"/>
+    <row r="19" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B4:C4"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B4:C4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>